--- a/output/pdf_financials_xlsx/RMES.xlsx
+++ b/output/pdf_financials_xlsx/RMES.xlsx
@@ -1082,13 +1082,13 @@
         </is>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.025699</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.264778</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>0.455165</v>
       </c>
     </row>
     <row r="35">
@@ -1124,13 +1124,13 @@
         </is>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.025699</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>0.264778</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>0.455165</v>
       </c>
     </row>
     <row r="37">
@@ -1376,13 +1376,13 @@
         </is>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0.025699</v>
+        <v>0</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>0.264778</v>
+        <v>0</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>0.455165</v>
+        <v>0</v>
       </c>
     </row>
     <row r="49">
@@ -3240,7 +3240,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">

--- a/output/pdf_financials_xlsx/RMES.xlsx
+++ b/output/pdf_financials_xlsx/RMES.xlsx
@@ -2655,10 +2655,10 @@
         <v>0</v>
       </c>
       <c r="D110" s="3" t="n">
-        <v>0</v>
+        <v>0.03822</v>
       </c>
       <c r="E110" s="3" t="n">
-        <v>0</v>
+        <v>0.06736499999999999</v>
       </c>
     </row>
     <row r="111">
@@ -2668,7 +2668,7 @@
         </is>
       </c>
       <c r="B111" s="3" t="n">
-        <v>0</v>
+        <v>-0.055572</v>
       </c>
       <c r="C111" s="3" t="n">
         <v>0</v>
@@ -3129,7 +3129,7 @@
         </is>
       </c>
       <c r="B134" s="3" t="n">
-        <v>0</v>
+        <v>-0.055572</v>
       </c>
       <c r="C134" s="3" t="n">
         <v>0</v>
@@ -3148,7 +3148,7 @@
         </is>
       </c>
       <c r="B135" s="3" t="n">
-        <v>-1.285255</v>
+        <v>-1.340827</v>
       </c>
       <c r="C135" s="3" t="n">
         <v>-0.161468</v>
@@ -4158,7 +4158,11 @@
           <t>Accretion</t>
         </is>
       </c>
-      <c r="D28" t="inlineStr"/>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>OtherNonCashItems</t>
+        </is>
+      </c>
       <c r="E28" t="inlineStr">
         <is>
           <t>-</t>
@@ -5026,7 +5030,11 @@
           <t>Accretion</t>
         </is>
       </c>
-      <c r="D53" t="inlineStr"/>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>OtherNonCashItems</t>
+        </is>
+      </c>
       <c r="E53" t="inlineStr">
         <is>
           <t>-</t>
@@ -5350,7 +5358,11 @@
           <t>Acquisition of equipment</t>
         </is>
       </c>
-      <c r="D62" t="inlineStr"/>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>PurchaseOfPPE</t>
+        </is>
+      </c>
       <c r="E62" s="5" t="n">
         <v>-0.055572</v>
       </c>
